--- a/balance_gen_add_data/input/loan_beh_models.xlsx
+++ b/balance_gen_add_data/input/loan_beh_models.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dzimi\Documents\data_engineering\data_projects\git_hub_projects\bank_project\balance_gen_add_data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{737C2E42-E733-40FE-8931-786AD74AEE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF92045E-FBAF-48AB-8B85-E0A8DB2EBB5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="4395" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3720" yWindow="3720" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="363">
   <si>
     <t>tenor</t>
   </si>
@@ -1122,6 +1122,9 @@
   </si>
   <si>
     <t>360M</t>
+  </si>
+  <si>
+    <t>report_date</t>
   </si>
 </sst>
 </file>
@@ -1169,7 +1172,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1450,35 +1453,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E362"/>
+  <dimension ref="A1:F362"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1">
+      <c r="C1" s="1">
         <v>1000</v>
       </c>
-      <c r="C1" s="1">
+      <c r="D1" s="1">
         <v>1100</v>
       </c>
-      <c r="D1" s="1">
+      <c r="E1" s="1">
         <v>2000</v>
       </c>
-      <c r="E1" s="1">
+      <c r="F1" s="1">
         <v>2100</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B2" t="s">
         <v>1</v>
-      </c>
-      <c r="B2" s="2">
-        <v>0</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1489,4396 +1495,5479 @@
       <c r="E2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C3">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D3">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E3">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="F3">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C4">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D4">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E4">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="F4">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C5">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D5">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E5">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="F5">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C6">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D6">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E6">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="F6">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C7">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D7">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E7">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="F7">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C8">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D8">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E8">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="F8">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C9">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D9">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E9">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="F9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C10">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D10">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E10">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="F10">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B11" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C11">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D11">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E11">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="F11">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C12">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D12">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E12">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="F12">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C13">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D13">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E13">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="F13">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C14">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D14">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E14">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="F14">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="2">
+      <c r="C15">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C15">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="D15">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E15">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="F15">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B16" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="2">
+      <c r="C16">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C16">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="D16">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E16">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="F16">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B17" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="2">
+      <c r="C17">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C17">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="D17">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E17">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="F17">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B18" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2">
+      <c r="C18">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C18">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="D18">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E18">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="F18">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B19" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="2">
+      <c r="C19">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C19">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="D19">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E19">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="F19">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B20" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="2">
+      <c r="C20">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C20">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="D20">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E20">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="F20">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B21" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="2">
+      <c r="C21">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C21">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="D21">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E21">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="F21">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B22" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="2">
+      <c r="C22">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C22">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="D22">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E22">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+      <c r="F22">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B23" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="2">
+      <c r="C23">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C23">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="D23">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E23">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+      <c r="F23">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B24" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="2">
+      <c r="C24">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C24">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="D24">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E24">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+      <c r="F24">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B25" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="2">
+      <c r="C25">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C25">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="D25">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E25">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+      <c r="F25">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B26" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="2">
+      <c r="C26">
         <v>0.02</v>
       </c>
-      <c r="C26">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="D26">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E26">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+      <c r="F26">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B27" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="2">
+      <c r="C27">
         <v>0.02</v>
       </c>
-      <c r="C27">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="D27">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E27">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+      <c r="F27">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B28" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="2">
+      <c r="C28">
         <v>0.02</v>
       </c>
-      <c r="C28">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="D28">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E28">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+      <c r="F28">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B29" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="2">
+      <c r="C29">
         <v>0.02</v>
       </c>
-      <c r="C29">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="D29">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E29">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+      <c r="F29">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B30" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="2">
+      <c r="C30">
         <v>0.02</v>
       </c>
-      <c r="C30">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="D30">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E30">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+      <c r="F30">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B31" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="2">
+      <c r="C31">
         <v>0.02</v>
       </c>
-      <c r="C31">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="D31">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E31">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+      <c r="F31">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B32" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="2">
+      <c r="C32">
         <v>0.02</v>
       </c>
-      <c r="C32">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="D32">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E32">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+      <c r="F32">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B33" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="2">
+      <c r="C33">
         <v>0.02</v>
       </c>
-      <c r="C33">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="D33">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E33">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+      <c r="F33">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B34" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="2">
+      <c r="C34">
         <v>0.02</v>
       </c>
-      <c r="C34">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="D34">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E34">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+      <c r="F34">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B35" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="2">
+      <c r="C35">
         <v>0.02</v>
       </c>
-      <c r="C35">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="D35">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E35">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+      <c r="F35">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B36" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="2">
+      <c r="C36">
         <v>0.02</v>
       </c>
-      <c r="C36">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="D36">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E36">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
+      <c r="F36">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B37" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="2">
+      <c r="C37">
         <v>0.02</v>
       </c>
-      <c r="C37">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="D37">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E37">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
+      <c r="F37">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B38" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="2">
+      <c r="C38">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C38">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="D38">
-        <v>2E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E38">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
+      <c r="F38">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B39" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="2">
+      <c r="C39">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>0.01</v>
       </c>
-      <c r="D39">
-        <v>2E-3</v>
-      </c>
       <c r="E39">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
+      <c r="F39">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B40" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="2">
+      <c r="C40">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>0.01</v>
       </c>
-      <c r="D40">
-        <v>2E-3</v>
-      </c>
       <c r="E40">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
+      <c r="F40">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B41" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="2">
+      <c r="C41">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>0.01</v>
       </c>
-      <c r="D41">
-        <v>2E-3</v>
-      </c>
       <c r="E41">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
+      <c r="F41">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B42" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="2">
+      <c r="C42">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>0.01</v>
       </c>
-      <c r="D42">
-        <v>2E-3</v>
-      </c>
       <c r="E42">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
+      <c r="F42">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B43" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="2">
+      <c r="C43">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>0.01</v>
       </c>
-      <c r="D43">
-        <v>2E-3</v>
-      </c>
       <c r="E43">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
+      <c r="F43">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B44" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="2">
+      <c r="C44">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>0.01</v>
       </c>
-      <c r="D44">
-        <v>2E-3</v>
-      </c>
       <c r="E44">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
+      <c r="F44">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B45" t="s">
         <v>44</v>
       </c>
-      <c r="B45" s="2">
+      <c r="C45">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C45">
+      <c r="D45">
         <v>0.01</v>
       </c>
-      <c r="D45">
-        <v>2E-3</v>
-      </c>
       <c r="E45">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
+      <c r="F45">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B46" t="s">
         <v>45</v>
       </c>
-      <c r="B46" s="2">
+      <c r="C46">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C46">
+      <c r="D46">
         <v>0.01</v>
       </c>
-      <c r="D46">
-        <v>2E-3</v>
-      </c>
       <c r="E46">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
+      <c r="F46">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B47" t="s">
         <v>46</v>
       </c>
-      <c r="B47" s="2">
+      <c r="C47">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>0.01</v>
       </c>
-      <c r="D47">
-        <v>2E-3</v>
-      </c>
       <c r="E47">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
+      <c r="F47">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B48" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="2">
+      <c r="C48">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>0.01</v>
       </c>
-      <c r="D48">
-        <v>2E-3</v>
-      </c>
       <c r="E48">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
+      <c r="F48">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B49" t="s">
         <v>48</v>
       </c>
-      <c r="B49" s="2">
+      <c r="C49">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C49">
+      <c r="D49">
         <v>0.01</v>
       </c>
-      <c r="D49">
-        <v>2E-3</v>
-      </c>
       <c r="E49">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
+      <c r="F49">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B50" t="s">
         <v>49</v>
       </c>
-      <c r="B50" s="2">
+      <c r="C50">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>0.01</v>
       </c>
-      <c r="D50">
-        <v>2E-3</v>
-      </c>
       <c r="E50">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
+      <c r="F50">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B51" t="s">
         <v>50</v>
       </c>
-      <c r="B51" s="2">
+      <c r="C51">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C51">
+      <c r="D51">
         <v>0.01</v>
       </c>
-      <c r="D51">
-        <v>2E-3</v>
-      </c>
       <c r="E51">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
+      <c r="F51">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B52" t="s">
         <v>51</v>
       </c>
-      <c r="B52" s="2">
+      <c r="C52">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C52">
+      <c r="D52">
         <v>0.01</v>
       </c>
-      <c r="D52">
-        <v>2E-3</v>
-      </c>
       <c r="E52">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
+      <c r="F52">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B53" t="s">
         <v>52</v>
       </c>
-      <c r="B53" s="2">
+      <c r="C53">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C53">
+      <c r="D53">
         <v>0.01</v>
       </c>
-      <c r="D53">
-        <v>2E-3</v>
-      </c>
       <c r="E53">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
+      <c r="F53">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B54" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="2">
+      <c r="C54">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C54">
+      <c r="D54">
         <v>0.01</v>
       </c>
-      <c r="D54">
-        <v>2E-3</v>
-      </c>
       <c r="E54">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
+      <c r="F54">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B55" t="s">
         <v>54</v>
       </c>
-      <c r="B55" s="2">
+      <c r="C55">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C55">
+      <c r="D55">
         <v>0.01</v>
       </c>
-      <c r="D55">
-        <v>2E-3</v>
-      </c>
       <c r="E55">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
+      <c r="F55">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B56" t="s">
         <v>55</v>
       </c>
-      <c r="B56" s="2">
+      <c r="C56">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C56">
+      <c r="D56">
         <v>0.01</v>
       </c>
-      <c r="D56">
-        <v>2E-3</v>
-      </c>
       <c r="E56">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
+      <c r="F56">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B57" t="s">
         <v>56</v>
       </c>
-      <c r="B57" s="2">
+      <c r="C57">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C57">
+      <c r="D57">
         <v>0.01</v>
       </c>
-      <c r="D57">
-        <v>2E-3</v>
-      </c>
       <c r="E57">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
+      <c r="F57">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B58" t="s">
         <v>57</v>
       </c>
-      <c r="B58" s="2">
+      <c r="C58">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C58">
+      <c r="D58">
         <v>0.01</v>
       </c>
-      <c r="D58">
-        <v>2E-3</v>
-      </c>
       <c r="E58">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
+      <c r="F58">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B59" t="s">
         <v>58</v>
       </c>
-      <c r="B59" s="2">
+      <c r="C59">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C59">
+      <c r="D59">
         <v>0.01</v>
       </c>
-      <c r="D59">
-        <v>2E-3</v>
-      </c>
       <c r="E59">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
+      <c r="F59">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B60" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="2">
+      <c r="C60">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C60">
+      <c r="D60">
         <v>0.01</v>
       </c>
-      <c r="D60">
-        <v>2E-3</v>
-      </c>
       <c r="E60">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
+      <c r="F60">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B61" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="2">
+      <c r="C61">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C61">
+      <c r="D61">
         <v>0.01</v>
       </c>
-      <c r="D61">
-        <v>2E-3</v>
-      </c>
       <c r="E61">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
+      <c r="F61">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A62" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B62" t="s">
         <v>61</v>
       </c>
-      <c r="B62" s="2">
+      <c r="C62">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C62">
+      <c r="D62">
         <v>0.01</v>
       </c>
-      <c r="D62">
-        <v>2E-3</v>
-      </c>
       <c r="E62">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
+      <c r="F62">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B63" t="s">
         <v>62</v>
       </c>
-      <c r="B63" s="2">
+      <c r="C63">
         <v>0.02</v>
       </c>
-      <c r="C63">
+      <c r="D63">
         <v>0.01</v>
       </c>
-      <c r="D63">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
+      <c r="E63">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A64" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B64" t="s">
         <v>63</v>
       </c>
-      <c r="B64" s="2">
+      <c r="C64">
         <v>0.02</v>
       </c>
-      <c r="C64">
+      <c r="D64">
         <v>0.01</v>
       </c>
-      <c r="D64">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
+      <c r="E64">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A65" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B65" t="s">
         <v>64</v>
       </c>
-      <c r="B65" s="2">
+      <c r="C65">
         <v>0.02</v>
       </c>
-      <c r="C65">
+      <c r="D65">
         <v>0.01</v>
       </c>
-      <c r="D65">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
+      <c r="E65">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A66" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B66" t="s">
         <v>65</v>
       </c>
-      <c r="B66" s="2">
+      <c r="C66">
         <v>0.02</v>
       </c>
-      <c r="C66">
+      <c r="D66">
         <v>0.01</v>
       </c>
-      <c r="D66">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
+      <c r="E66">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A67" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B67" t="s">
         <v>66</v>
       </c>
-      <c r="B67" s="2">
+      <c r="C67">
         <v>0.02</v>
       </c>
-      <c r="C67">
+      <c r="D67">
         <v>0.01</v>
       </c>
-      <c r="D67">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
+      <c r="E67">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A68" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B68" t="s">
         <v>67</v>
       </c>
-      <c r="B68" s="2">
+      <c r="C68">
         <v>0.02</v>
       </c>
-      <c r="C68">
+      <c r="D68">
         <v>0.01</v>
       </c>
-      <c r="D68">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
+      <c r="E68">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A69" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B69" t="s">
         <v>68</v>
       </c>
-      <c r="B69" s="2">
+      <c r="C69">
         <v>0.02</v>
       </c>
-      <c r="C69">
+      <c r="D69">
         <v>0.01</v>
       </c>
-      <c r="D69">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
+      <c r="E69">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A70" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B70" t="s">
         <v>69</v>
       </c>
-      <c r="B70" s="2">
+      <c r="C70">
         <v>0.02</v>
       </c>
-      <c r="C70">
+      <c r="D70">
         <v>0.01</v>
       </c>
-      <c r="D70">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
+      <c r="E70">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B71" t="s">
         <v>70</v>
       </c>
-      <c r="B71" s="2">
+      <c r="C71">
         <v>0.02</v>
       </c>
-      <c r="C71">
+      <c r="D71">
         <v>0.01</v>
       </c>
-      <c r="D71">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
+      <c r="E71">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B72" t="s">
         <v>71</v>
       </c>
-      <c r="B72" s="2">
+      <c r="C72">
         <v>0.02</v>
       </c>
-      <c r="C72">
+      <c r="D72">
         <v>0.01</v>
       </c>
-      <c r="D72">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
+      <c r="E72">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A73" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B73" t="s">
         <v>72</v>
       </c>
-      <c r="B73" s="2">
+      <c r="C73">
         <v>0.02</v>
       </c>
-      <c r="C73">
+      <c r="D73">
         <v>0.01</v>
       </c>
-      <c r="D73">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
+      <c r="E73">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A74" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B74" t="s">
         <v>73</v>
       </c>
-      <c r="B74" s="2">
+      <c r="C74">
         <v>0.02</v>
       </c>
-      <c r="C74">
+      <c r="D74">
         <v>0.01</v>
       </c>
-      <c r="D74">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
+      <c r="E74">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A75" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B75" t="s">
         <v>74</v>
       </c>
-      <c r="B75" s="2">
+      <c r="C75">
         <v>0.02</v>
       </c>
-      <c r="C75">
+      <c r="D75">
         <v>0.01</v>
       </c>
-      <c r="D75">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
+      <c r="E75">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A76" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B76" t="s">
         <v>75</v>
       </c>
-      <c r="B76" s="2">
+      <c r="C76">
         <v>0.02</v>
       </c>
-      <c r="C76">
+      <c r="D76">
         <v>0.01</v>
       </c>
-      <c r="D76">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
+      <c r="E76">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A77" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B77" t="s">
         <v>76</v>
       </c>
-      <c r="B77" s="2">
+      <c r="C77">
         <v>0.02</v>
       </c>
-      <c r="C77">
+      <c r="D77">
         <v>0.01</v>
       </c>
-      <c r="D77">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
+      <c r="E77">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A78" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B78" t="s">
         <v>77</v>
       </c>
-      <c r="B78" s="2">
+      <c r="C78">
         <v>0.02</v>
       </c>
-      <c r="C78">
+      <c r="D78">
         <v>0.01</v>
       </c>
-      <c r="D78">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
+      <c r="E78">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A79" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B79" t="s">
         <v>78</v>
       </c>
-      <c r="B79" s="2">
+      <c r="C79">
         <v>0.02</v>
       </c>
-      <c r="C79">
+      <c r="D79">
         <v>0.01</v>
       </c>
-      <c r="D79">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
+      <c r="E79">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B80" t="s">
         <v>79</v>
       </c>
-      <c r="B80" s="2">
+      <c r="C80">
         <v>0.02</v>
       </c>
-      <c r="C80">
+      <c r="D80">
         <v>0.01</v>
       </c>
-      <c r="D80">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
+      <c r="E80">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A81" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B81" t="s">
         <v>80</v>
       </c>
-      <c r="B81" s="2">
+      <c r="C81">
         <v>0.02</v>
       </c>
-      <c r="C81">
+      <c r="D81">
         <v>0.01</v>
       </c>
-      <c r="D81">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
+      <c r="E81">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A82" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B82" t="s">
         <v>81</v>
       </c>
-      <c r="B82" s="2">
+      <c r="C82">
         <v>0.02</v>
       </c>
-      <c r="C82">
+      <c r="D82">
         <v>0.01</v>
       </c>
-      <c r="D82">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
+      <c r="E82">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A83" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B83" t="s">
         <v>82</v>
       </c>
-      <c r="B83" s="2">
+      <c r="C83">
         <v>0.02</v>
       </c>
-      <c r="C83">
+      <c r="D83">
         <v>0.01</v>
       </c>
-      <c r="D83">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
+      <c r="E83">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A84" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B84" t="s">
         <v>83</v>
       </c>
-      <c r="B84" s="2">
+      <c r="C84">
         <v>0.02</v>
       </c>
-      <c r="C84">
+      <c r="D84">
         <v>0.01</v>
       </c>
-      <c r="D84">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
+      <c r="E84">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A85" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B85" t="s">
         <v>84</v>
       </c>
-      <c r="B85" s="2">
+      <c r="C85">
         <v>0.02</v>
       </c>
-      <c r="C85">
+      <c r="D85">
         <v>0.01</v>
       </c>
-      <c r="D85">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
+      <c r="E85">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A86" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B86" t="s">
         <v>85</v>
       </c>
-      <c r="B86" s="2">
+      <c r="C86">
         <v>0.02</v>
       </c>
-      <c r="C86">
+      <c r="D86">
         <v>0.01</v>
       </c>
-      <c r="D86">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
+      <c r="E86">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A87" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B87" t="s">
         <v>86</v>
       </c>
-      <c r="B87" s="2">
+      <c r="C87">
         <v>0.02</v>
       </c>
-      <c r="C87">
+      <c r="D87">
         <v>0.01</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A88" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B88" t="s">
         <v>87</v>
       </c>
-      <c r="B88" s="2">
+      <c r="C88">
         <v>0.02</v>
       </c>
-      <c r="C88">
+      <c r="D88">
         <v>0.01</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A89" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B89" t="s">
         <v>88</v>
       </c>
-      <c r="B89" s="2">
+      <c r="C89">
         <v>0.02</v>
       </c>
-      <c r="C89">
+      <c r="D89">
         <v>0.01</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A90" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B90" t="s">
         <v>89</v>
       </c>
-      <c r="B90" s="2">
+      <c r="C90">
         <v>0.02</v>
       </c>
-      <c r="C90">
+      <c r="D90">
         <v>0.01</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A91" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B91" t="s">
         <v>90</v>
       </c>
-      <c r="B91" s="2">
+      <c r="C91">
         <v>0.02</v>
       </c>
-      <c r="C91">
+      <c r="D91">
         <v>0.01</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A92" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B92" t="s">
         <v>91</v>
       </c>
-      <c r="B92" s="2">
+      <c r="C92">
         <v>0.02</v>
       </c>
-      <c r="C92">
+      <c r="D92">
         <v>0.01</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A93" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B93" t="s">
         <v>92</v>
       </c>
-      <c r="B93" s="2">
+      <c r="C93">
         <v>0.02</v>
       </c>
-      <c r="C93">
+      <c r="D93">
         <v>0.01</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A94" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B94" t="s">
         <v>93</v>
       </c>
-      <c r="B94" s="2">
+      <c r="C94">
         <v>0.02</v>
       </c>
-      <c r="C94">
+      <c r="D94">
         <v>0.01</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A95" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B95" t="s">
         <v>94</v>
       </c>
-      <c r="B95" s="2">
+      <c r="C95">
         <v>0.02</v>
       </c>
-      <c r="C95">
+      <c r="D95">
         <v>0.01</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A96" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B96" t="s">
         <v>95</v>
       </c>
-      <c r="B96" s="2">
+      <c r="C96">
         <v>0.02</v>
       </c>
-      <c r="C96">
+      <c r="D96">
         <v>0.01</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B97" t="s">
         <v>96</v>
       </c>
-      <c r="B97" s="2">
+      <c r="C97">
         <v>0.02</v>
       </c>
-      <c r="C97">
+      <c r="D97">
         <v>0.01</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B98" t="s">
         <v>97</v>
       </c>
-      <c r="B98" s="2">
+      <c r="C98">
         <v>0.02</v>
       </c>
-      <c r="C98">
+      <c r="D98">
         <v>0.01</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A99" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B99" t="s">
         <v>98</v>
       </c>
-      <c r="B99" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C99">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
+      <c r="D99">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A100" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B100" t="s">
         <v>99</v>
       </c>
-      <c r="B100" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C100">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
+      <c r="D100">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A101" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B101" t="s">
         <v>100</v>
       </c>
-      <c r="B101" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C101">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
+      <c r="D101">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A102" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B102" t="s">
         <v>101</v>
       </c>
-      <c r="B102" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C102">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
+      <c r="D102">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A103" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B103" t="s">
         <v>102</v>
       </c>
-      <c r="B103" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C103">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
+      <c r="D103">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A104" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B104" t="s">
         <v>103</v>
       </c>
-      <c r="B104" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C104">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
+      <c r="D104">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A105" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B105" t="s">
         <v>104</v>
       </c>
-      <c r="B105" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C105">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
+      <c r="D105">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A106" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B106" t="s">
         <v>105</v>
       </c>
-      <c r="B106" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C106">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
+      <c r="D106">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A107" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B107" t="s">
         <v>106</v>
       </c>
-      <c r="B107" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C107">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
+      <c r="D107">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A108" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B108" t="s">
         <v>107</v>
       </c>
-      <c r="B108" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C108">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
+      <c r="D108">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A109" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B109" t="s">
         <v>108</v>
       </c>
-      <c r="B109" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C109">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
+      <c r="D109">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A110" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B110" t="s">
         <v>109</v>
       </c>
-      <c r="B110" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C110">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
+      <c r="D110">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A111" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B111" t="s">
         <v>110</v>
       </c>
-      <c r="B111" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C111">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
+      <c r="D111">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A112" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B112" t="s">
         <v>111</v>
       </c>
-      <c r="B112" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C112">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
+      <c r="D112">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A113" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B113" t="s">
         <v>112</v>
       </c>
-      <c r="B113" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C113">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A114" t="s">
+      <c r="D113">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A114" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B114" t="s">
         <v>113</v>
       </c>
-      <c r="B114" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C114">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
+      <c r="D114">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A115" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B115" t="s">
         <v>114</v>
       </c>
-      <c r="B115" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C115">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
+      <c r="D115">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A116" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B116" t="s">
         <v>115</v>
       </c>
-      <c r="B116" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C116">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A117" t="s">
+      <c r="D116">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A117" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B117" t="s">
         <v>116</v>
       </c>
-      <c r="B117" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C117">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A118" t="s">
+      <c r="D117">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A118" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B118" t="s">
         <v>117</v>
       </c>
-      <c r="B118" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C118">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A119" t="s">
+      <c r="D118">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A119" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B119" t="s">
         <v>118</v>
       </c>
-      <c r="B119" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C119">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
+      <c r="D119">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A120" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B120" t="s">
         <v>119</v>
       </c>
-      <c r="B120" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C120">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A121" t="s">
+      <c r="D120">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A121" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B121" t="s">
         <v>120</v>
       </c>
-      <c r="B121" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C121">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
+      <c r="D121">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A122" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B122" t="s">
         <v>121</v>
       </c>
-      <c r="B122" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C122">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A123" t="s">
+      <c r="D122">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A123" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B123" t="s">
         <v>122</v>
       </c>
-      <c r="B123" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C123">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A124" t="s">
+      <c r="D123">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A124" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B124" t="s">
         <v>123</v>
       </c>
-      <c r="B124" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C124">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
+      <c r="D124">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A125" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B125" t="s">
         <v>124</v>
       </c>
-      <c r="B125" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C125">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A126" t="s">
+      <c r="D125">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A126" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B126" t="s">
         <v>125</v>
       </c>
-      <c r="B126" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C126">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A127" t="s">
+      <c r="D126">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A127" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B127" t="s">
         <v>126</v>
       </c>
-      <c r="B127" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C127">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A128" t="s">
+      <c r="D127">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A128" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B128" t="s">
         <v>127</v>
       </c>
-      <c r="B128" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C128">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A129" t="s">
+      <c r="D128">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A129" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B129" t="s">
         <v>128</v>
       </c>
-      <c r="B129" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C129">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A130" t="s">
+      <c r="D129">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A130" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B130" t="s">
         <v>129</v>
       </c>
-      <c r="B130" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C130">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A131" t="s">
+      <c r="D130">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A131" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B131" t="s">
         <v>130</v>
       </c>
-      <c r="B131" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C131">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A132" t="s">
+      <c r="D131">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A132" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B132" t="s">
         <v>131</v>
       </c>
-      <c r="B132" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C132">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A133" t="s">
+      <c r="D132">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A133" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B133" t="s">
         <v>132</v>
       </c>
-      <c r="B133" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C133">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A134" t="s">
+      <c r="D133">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A134" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B134" t="s">
         <v>133</v>
       </c>
-      <c r="B134" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C134">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A135" t="s">
+      <c r="D134">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A135" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B135" t="s">
         <v>134</v>
       </c>
-      <c r="B135" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C135">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A136" t="s">
+      <c r="D135">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A136" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B136" t="s">
         <v>135</v>
       </c>
-      <c r="B136" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C136">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
+      <c r="D136">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A137" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B137" t="s">
         <v>136</v>
       </c>
-      <c r="B137" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C137">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A138" t="s">
+      <c r="D137">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A138" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B138" t="s">
         <v>137</v>
       </c>
-      <c r="B138" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C138">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A139" t="s">
+      <c r="D138">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A139" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B139" t="s">
         <v>138</v>
       </c>
-      <c r="B139" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C139">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
+      <c r="D139">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A140" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B140" t="s">
         <v>139</v>
       </c>
-      <c r="B140" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C140">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
+      <c r="D140">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A141" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B141" t="s">
         <v>140</v>
       </c>
-      <c r="B141" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C141">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A142" t="s">
+      <c r="D141">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A142" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B142" t="s">
         <v>141</v>
       </c>
-      <c r="B142" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C142">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A143" t="s">
+      <c r="D142">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A143" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B143" t="s">
         <v>142</v>
       </c>
-      <c r="B143" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C143">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
+      <c r="D143">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A144" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B144" t="s">
         <v>143</v>
       </c>
-      <c r="B144" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C144">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A145" t="s">
+      <c r="D144">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A145" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B145" t="s">
         <v>144</v>
       </c>
-      <c r="B145" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C145">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A146" t="s">
+      <c r="D145">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A146" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B146" t="s">
         <v>145</v>
       </c>
-      <c r="B146" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C146">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A147" t="s">
+      <c r="D146">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A147" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B147" t="s">
         <v>146</v>
       </c>
-      <c r="B147" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C147">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A148" t="s">
+      <c r="D147">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A148" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B148" t="s">
         <v>147</v>
       </c>
-      <c r="B148" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C148">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
+      <c r="D148">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A149" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B149" t="s">
         <v>148</v>
       </c>
-      <c r="B149" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C149">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A150" t="s">
+      <c r="D149">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A150" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B150" t="s">
         <v>149</v>
       </c>
-      <c r="B150" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C150">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A151" t="s">
+      <c r="D150">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A151" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B151" t="s">
         <v>150</v>
       </c>
-      <c r="B151" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C151">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A152" t="s">
+      <c r="D151">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A152" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B152" t="s">
         <v>151</v>
       </c>
-      <c r="B152" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C152">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A153" t="s">
+      <c r="D152">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A153" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B153" t="s">
         <v>152</v>
       </c>
-      <c r="B153" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C153">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A154" t="s">
+      <c r="D153">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A154" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B154" t="s">
         <v>153</v>
       </c>
-      <c r="B154" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C154">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A155" t="s">
+      <c r="D154">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A155" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B155" t="s">
         <v>154</v>
       </c>
-      <c r="B155" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C155">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A156" t="s">
+      <c r="D155">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A156" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B156" t="s">
         <v>155</v>
       </c>
-      <c r="B156" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C156">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A157" t="s">
+      <c r="D156">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A157" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B157" t="s">
         <v>156</v>
       </c>
-      <c r="B157" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C157">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A158" t="s">
+      <c r="D157">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A158" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B158" t="s">
         <v>157</v>
       </c>
-      <c r="B158" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C158">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A159" t="s">
+      <c r="D158">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A159" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B159" t="s">
         <v>158</v>
       </c>
-      <c r="B159" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C159">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A160" t="s">
+      <c r="D159">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A160" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B160" t="s">
         <v>159</v>
       </c>
-      <c r="B160" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C160">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A161" t="s">
+      <c r="D160">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A161" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B161" t="s">
         <v>160</v>
       </c>
-      <c r="B161" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C161">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A162" t="s">
+      <c r="D161">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A162" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B162" t="s">
         <v>161</v>
       </c>
-      <c r="B162" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C162">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A163" t="s">
+      <c r="D162">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A163" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B163" t="s">
         <v>162</v>
       </c>
-      <c r="B163" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C163">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A164" t="s">
+      <c r="D163">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A164" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B164" t="s">
         <v>163</v>
       </c>
-      <c r="B164" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C164">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A165" t="s">
+      <c r="D164">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A165" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B165" t="s">
         <v>164</v>
       </c>
-      <c r="B165" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C165">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A166" t="s">
+      <c r="D165">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A166" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B166" t="s">
         <v>165</v>
       </c>
-      <c r="B166" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C166">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A167" t="s">
+      <c r="D166">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A167" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B167" t="s">
         <v>166</v>
       </c>
-      <c r="B167" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C167">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A168" t="s">
+      <c r="D167">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A168" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B168" t="s">
         <v>167</v>
       </c>
-      <c r="B168" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C168">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A169" t="s">
+      <c r="D168">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A169" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B169" t="s">
         <v>168</v>
       </c>
-      <c r="B169" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C169">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A170" t="s">
+      <c r="D169">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A170" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B170" t="s">
         <v>169</v>
       </c>
-      <c r="B170" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C170">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A171" t="s">
+      <c r="D170">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A171" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B171" t="s">
         <v>170</v>
       </c>
-      <c r="B171" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C171">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A172" t="s">
+      <c r="D171">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A172" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B172" t="s">
         <v>171</v>
       </c>
-      <c r="B172" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C172">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A173" t="s">
+      <c r="D172">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A173" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B173" t="s">
         <v>172</v>
       </c>
-      <c r="B173" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C173">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A174" t="s">
+      <c r="D173">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A174" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B174" t="s">
         <v>173</v>
       </c>
-      <c r="B174" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C174">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A175" t="s">
+      <c r="D174">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A175" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B175" t="s">
         <v>174</v>
       </c>
-      <c r="B175" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C175">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A176" t="s">
+      <c r="D175">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A176" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B176" t="s">
         <v>175</v>
       </c>
-      <c r="B176" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C176">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A177" t="s">
+      <c r="D176">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A177" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B177" t="s">
         <v>176</v>
       </c>
-      <c r="B177" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C177">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A178" t="s">
+      <c r="D177">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A178" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B178" t="s">
         <v>177</v>
       </c>
-      <c r="B178" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C178">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A179" t="s">
+      <c r="D178">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A179" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B179" t="s">
         <v>178</v>
       </c>
-      <c r="B179" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C179">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A180" t="s">
+      <c r="D179">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A180" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B180" t="s">
         <v>179</v>
       </c>
-      <c r="B180" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C180">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A181" t="s">
+      <c r="D180">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A181" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B181" t="s">
         <v>180</v>
       </c>
-      <c r="B181" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C181">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A182" t="s">
+      <c r="D181">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A182" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B182" t="s">
         <v>181</v>
       </c>
-      <c r="B182" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C182">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A183" t="s">
+      <c r="D182">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A183" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B183" t="s">
         <v>182</v>
       </c>
-      <c r="B183" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C183">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A184" t="s">
+      <c r="D183">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A184" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B184" t="s">
         <v>183</v>
       </c>
-      <c r="B184" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C184">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A185" t="s">
+      <c r="D184">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A185" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B185" t="s">
         <v>184</v>
       </c>
-      <c r="B185" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C185">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A186" t="s">
+      <c r="D185">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A186" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B186" t="s">
         <v>185</v>
       </c>
-      <c r="B186" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C186">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A187" t="s">
+      <c r="D186">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A187" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B187" t="s">
         <v>186</v>
       </c>
-      <c r="B187" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C187">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A188" t="s">
+      <c r="D187">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A188" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B188" t="s">
         <v>187</v>
       </c>
-      <c r="B188" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C188">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A189" t="s">
+      <c r="D188">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A189" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B189" t="s">
         <v>188</v>
       </c>
-      <c r="B189" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C189">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A190" t="s">
+      <c r="D189">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A190" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B190" t="s">
         <v>189</v>
       </c>
-      <c r="B190" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C190">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A191" t="s">
+      <c r="D190">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A191" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B191" t="s">
         <v>190</v>
       </c>
-      <c r="B191" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C191">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A192" t="s">
+      <c r="D191">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A192" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B192" t="s">
         <v>191</v>
       </c>
-      <c r="B192" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C192">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A193" t="s">
+      <c r="D192">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A193" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B193" t="s">
         <v>192</v>
       </c>
-      <c r="B193" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C193">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A194" t="s">
+      <c r="D193">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A194" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B194" t="s">
         <v>193</v>
       </c>
-      <c r="B194" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C194">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A195" t="s">
+      <c r="D194">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A195" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B195" t="s">
         <v>194</v>
       </c>
-      <c r="B195" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C195">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A196" t="s">
+      <c r="D195">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A196" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B196" t="s">
         <v>195</v>
       </c>
-      <c r="B196" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C196">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A197" t="s">
+      <c r="D196">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A197" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B197" t="s">
         <v>196</v>
       </c>
-      <c r="B197" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C197">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A198" t="s">
+      <c r="D197">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A198" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B198" t="s">
         <v>197</v>
       </c>
-      <c r="B198" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C198">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A199" t="s">
+      <c r="D198">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A199" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B199" t="s">
         <v>198</v>
       </c>
-      <c r="B199" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C199">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A200" t="s">
+      <c r="D199">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A200" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B200" t="s">
         <v>199</v>
       </c>
-      <c r="B200" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C200">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A201" t="s">
+      <c r="D200">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A201" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B201" t="s">
         <v>200</v>
       </c>
-      <c r="B201" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C201">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A202" t="s">
+      <c r="D201">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A202" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B202" t="s">
         <v>201</v>
       </c>
-      <c r="B202" s="2">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C202">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A203" t="s">
+      <c r="D202">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A203" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B203" t="s">
         <v>202</v>
       </c>
-      <c r="B203" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C203">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A204" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D203">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A204" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B204" t="s">
         <v>203</v>
       </c>
-      <c r="B204" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C204">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A205" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D204">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A205" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B205" t="s">
         <v>204</v>
       </c>
-      <c r="B205" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C205">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A206" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D205">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A206" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B206" t="s">
         <v>205</v>
       </c>
-      <c r="B206" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C206">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A207" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D206">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A207" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B207" t="s">
         <v>206</v>
       </c>
-      <c r="B207" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C207">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A208" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D207">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A208" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B208" t="s">
         <v>207</v>
       </c>
-      <c r="B208" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C208">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A209" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D208">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A209" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B209" t="s">
         <v>208</v>
       </c>
-      <c r="B209" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C209">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A210" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D209">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A210" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B210" t="s">
         <v>209</v>
       </c>
-      <c r="B210" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C210">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A211" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D210">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A211" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B211" t="s">
         <v>210</v>
       </c>
-      <c r="B211" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C211">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A212" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D211">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A212" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B212" t="s">
         <v>211</v>
       </c>
-      <c r="B212" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C212">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A213" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D212">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A213" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B213" t="s">
         <v>212</v>
       </c>
-      <c r="B213" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C213">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A214" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D213">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A214" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B214" t="s">
         <v>213</v>
       </c>
-      <c r="B214" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C214">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A215" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D214">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A215" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B215" t="s">
         <v>214</v>
       </c>
-      <c r="B215" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C215">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A216" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D215">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A216" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B216" t="s">
         <v>215</v>
       </c>
-      <c r="B216" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C216">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A217" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D216">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A217" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B217" t="s">
         <v>216</v>
       </c>
-      <c r="B217" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C217">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A218" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D217">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A218" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B218" t="s">
         <v>217</v>
       </c>
-      <c r="B218" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C218">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A219" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D218">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A219" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B219" t="s">
         <v>218</v>
       </c>
-      <c r="B219" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C219">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A220" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D219">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A220" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B220" t="s">
         <v>219</v>
       </c>
-      <c r="B220" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C220">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A221" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D220">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A221" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B221" t="s">
         <v>220</v>
       </c>
-      <c r="B221" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C221">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A222" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D221">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A222" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B222" t="s">
         <v>221</v>
       </c>
-      <c r="B222" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C222">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A223" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D222">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A223" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B223" t="s">
         <v>222</v>
       </c>
-      <c r="B223" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C223">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A224" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D223">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A224" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B224" t="s">
         <v>223</v>
       </c>
-      <c r="B224" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C224">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A225" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D224">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A225" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B225" t="s">
         <v>224</v>
       </c>
-      <c r="B225" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C225">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A226" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D225">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A226" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B226" t="s">
         <v>225</v>
       </c>
-      <c r="B226" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C226">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A227" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D226">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A227" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B227" t="s">
         <v>226</v>
       </c>
-      <c r="B227" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C227">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A228" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D227">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A228" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B228" t="s">
         <v>227</v>
       </c>
-      <c r="B228" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C228">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A229" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D228">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A229" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B229" t="s">
         <v>228</v>
       </c>
-      <c r="B229" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C229">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A230" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D229">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A230" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B230" t="s">
         <v>229</v>
       </c>
-      <c r="B230" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C230">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A231" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D230">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A231" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B231" t="s">
         <v>230</v>
       </c>
-      <c r="B231" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C231">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A232" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D231">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A232" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B232" t="s">
         <v>231</v>
       </c>
-      <c r="B232" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C232">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A233" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D232">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A233" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B233" t="s">
         <v>232</v>
       </c>
-      <c r="B233" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C233">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A234" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D233">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A234" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B234" t="s">
         <v>233</v>
       </c>
-      <c r="B234" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C234">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A235" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D234">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A235" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B235" t="s">
         <v>234</v>
       </c>
-      <c r="B235" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C235">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A236" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D235">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A236" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B236" t="s">
         <v>235</v>
       </c>
-      <c r="B236" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C236">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A237" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D236">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A237" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B237" t="s">
         <v>236</v>
       </c>
-      <c r="B237" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C237">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A238" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D237">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A238" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B238" t="s">
         <v>237</v>
       </c>
-      <c r="B238" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C238">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A239" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D238">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A239" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B239" t="s">
         <v>238</v>
       </c>
-      <c r="B239" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C239">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A240" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D239">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A240" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B240" t="s">
         <v>239</v>
       </c>
-      <c r="B240" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C240">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A241" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D240">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A241" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B241" t="s">
         <v>240</v>
       </c>
-      <c r="B241" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C241">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A242" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D241">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A242" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B242" t="s">
         <v>241</v>
       </c>
-      <c r="B242" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C242">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A243" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D242">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A243" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B243" t="s">
         <v>242</v>
       </c>
-      <c r="B243" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C243">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A244" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D243">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A244" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B244" t="s">
         <v>243</v>
       </c>
-      <c r="B244" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C244">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A245" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D244">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A245" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B245" t="s">
         <v>244</v>
       </c>
-      <c r="B245" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C245">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A246" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D245">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A246" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B246" t="s">
         <v>245</v>
       </c>
-      <c r="B246" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C246">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A247" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D246">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A247" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B247" t="s">
         <v>246</v>
       </c>
-      <c r="B247" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C247">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A248" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D247">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A248" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B248" t="s">
         <v>247</v>
       </c>
-      <c r="B248" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C248">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A249" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D248">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A249" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B249" t="s">
         <v>248</v>
       </c>
-      <c r="B249" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C249">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A250" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D249">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A250" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B250" t="s">
         <v>249</v>
       </c>
-      <c r="B250" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C250">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A251" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D250">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A251" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B251" t="s">
         <v>250</v>
       </c>
-      <c r="B251" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C251">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A252" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D251">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A252" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B252" t="s">
         <v>251</v>
       </c>
-      <c r="B252" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C252">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A253" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D252">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A253" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B253" t="s">
         <v>252</v>
       </c>
-      <c r="B253" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C253">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A254" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D253">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A254" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B254" t="s">
         <v>253</v>
       </c>
-      <c r="B254" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C254">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A255" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D254">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A255" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B255" t="s">
         <v>254</v>
       </c>
-      <c r="B255" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C255">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A256" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D255">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A256" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B256" t="s">
         <v>255</v>
       </c>
-      <c r="B256" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C256">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A257" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D256">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A257" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B257" t="s">
         <v>256</v>
       </c>
-      <c r="B257" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C257">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A258" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D257">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A258" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B258" t="s">
         <v>257</v>
       </c>
-      <c r="B258" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C258">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A259" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D258">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A259" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B259" t="s">
         <v>258</v>
       </c>
-      <c r="B259" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C259">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A260" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D259">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A260" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B260" t="s">
         <v>259</v>
       </c>
-      <c r="B260" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C260">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A261" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D260">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A261" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B261" t="s">
         <v>260</v>
       </c>
-      <c r="B261" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C261">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A262" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D261">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A262" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B262" t="s">
         <v>261</v>
       </c>
-      <c r="B262" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C262">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A263" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D262">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A263" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B263" t="s">
         <v>262</v>
       </c>
-      <c r="B263" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C263">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A264" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D263">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A264" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B264" t="s">
         <v>263</v>
       </c>
-      <c r="B264" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C264">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A265" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D264">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A265" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B265" t="s">
         <v>264</v>
       </c>
-      <c r="B265" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C265">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A266" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D265">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A266" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B266" t="s">
         <v>265</v>
       </c>
-      <c r="B266" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C266">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A267" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D266">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A267" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B267" t="s">
         <v>266</v>
       </c>
-      <c r="B267" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C267">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A268" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D267">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A268" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B268" t="s">
         <v>267</v>
       </c>
-      <c r="B268" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C268">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A269" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D268">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A269" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B269" t="s">
         <v>268</v>
       </c>
-      <c r="B269" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C269">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A270" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D269">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A270" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B270" t="s">
         <v>269</v>
       </c>
-      <c r="B270" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C270">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A271" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D270">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A271" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B271" t="s">
         <v>270</v>
       </c>
-      <c r="B271" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C271">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A272" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D271">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A272" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B272" t="s">
         <v>271</v>
       </c>
-      <c r="B272" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C272">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A273" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D272">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A273" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B273" t="s">
         <v>272</v>
       </c>
-      <c r="B273" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C273">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A274" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D273">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A274" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B274" t="s">
         <v>273</v>
       </c>
-      <c r="B274" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C274">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A275" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D274">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A275" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B275" t="s">
         <v>274</v>
       </c>
-      <c r="B275" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C275">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A276" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D275">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A276" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B276" t="s">
         <v>275</v>
       </c>
-      <c r="B276" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C276">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A277" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D276">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A277" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B277" t="s">
         <v>276</v>
       </c>
-      <c r="B277" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C277">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A278" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D277">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A278" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B278" t="s">
         <v>277</v>
       </c>
-      <c r="B278" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C278">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A279" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D278">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A279" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B279" t="s">
         <v>278</v>
       </c>
-      <c r="B279" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C279">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A280" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D279">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A280" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B280" t="s">
         <v>279</v>
       </c>
-      <c r="B280" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C280">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A281" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D280">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A281" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B281" t="s">
         <v>280</v>
       </c>
-      <c r="B281" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C281">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A282" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D281">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A282" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B282" t="s">
         <v>281</v>
       </c>
-      <c r="B282" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C282">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A283" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D282">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A283" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B283" t="s">
         <v>282</v>
       </c>
-      <c r="B283" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C283">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A284" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D283">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A284" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B284" t="s">
         <v>283</v>
       </c>
-      <c r="B284" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C284">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A285" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D284">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A285" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B285" t="s">
         <v>284</v>
       </c>
-      <c r="B285" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C285">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A286" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D285">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A286" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B286" t="s">
         <v>285</v>
       </c>
-      <c r="B286" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C286">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A287" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D286">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A287" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B287" t="s">
         <v>286</v>
       </c>
-      <c r="B287" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C287">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A288" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D287">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A288" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B288" t="s">
         <v>287</v>
       </c>
-      <c r="B288" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C288">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A289" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D288">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A289" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B289" t="s">
         <v>288</v>
       </c>
-      <c r="B289" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C289">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A290" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D289">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A290" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B290" t="s">
         <v>289</v>
       </c>
-      <c r="B290" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C290">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A291" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D290">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A291" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B291" t="s">
         <v>290</v>
       </c>
-      <c r="B291" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C291">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A292" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D291">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A292" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B292" t="s">
         <v>291</v>
       </c>
-      <c r="B292" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C292">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A293" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D292">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A293" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B293" t="s">
         <v>292</v>
       </c>
-      <c r="B293" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C293">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A294" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D293">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A294" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B294" t="s">
         <v>293</v>
       </c>
-      <c r="B294" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C294">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A295" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D294">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A295" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B295" t="s">
         <v>294</v>
       </c>
-      <c r="B295" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C295">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A296" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D295">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A296" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B296" t="s">
         <v>295</v>
       </c>
-      <c r="B296" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C296">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A297" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D296">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A297" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B297" t="s">
         <v>296</v>
       </c>
-      <c r="B297" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C297">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A298" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D297">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A298" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B298" t="s">
         <v>297</v>
       </c>
-      <c r="B298" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C298">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A299" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D298">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A299" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B299" t="s">
         <v>298</v>
       </c>
-      <c r="B299" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C299">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A300" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D299">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A300" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B300" t="s">
         <v>299</v>
       </c>
-      <c r="B300" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C300">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A301" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D300">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A301" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B301" t="s">
         <v>300</v>
       </c>
-      <c r="B301" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C301">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A302" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D301">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A302" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B302" t="s">
         <v>301</v>
       </c>
-      <c r="B302" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C302">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A303" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D302">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A303" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B303" t="s">
         <v>302</v>
       </c>
-      <c r="B303" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C303">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A304" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D303">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A304" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B304" t="s">
         <v>303</v>
       </c>
-      <c r="B304" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C304">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A305" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D304">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A305" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B305" t="s">
         <v>304</v>
       </c>
-      <c r="B305" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C305">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A306" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D305">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A306" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B306" t="s">
         <v>305</v>
       </c>
-      <c r="B306" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C306">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A307" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D306">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A307" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B307" t="s">
         <v>306</v>
       </c>
-      <c r="B307" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C307">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A308" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D307">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A308" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B308" t="s">
         <v>307</v>
       </c>
-      <c r="B308" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C308">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A309" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D308">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A309" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B309" t="s">
         <v>308</v>
       </c>
-      <c r="B309" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C309">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A310" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D309">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A310" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B310" t="s">
         <v>309</v>
       </c>
-      <c r="B310" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C310">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A311" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D310">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A311" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B311" t="s">
         <v>310</v>
       </c>
-      <c r="B311" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C311">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A312" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D311">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A312" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B312" t="s">
         <v>311</v>
       </c>
-      <c r="B312" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C312">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A313" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D312">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A313" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B313" t="s">
         <v>312</v>
       </c>
-      <c r="B313" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C313">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A314" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D313">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A314" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B314" t="s">
         <v>313</v>
       </c>
-      <c r="B314" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C314">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A315" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D314">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A315" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B315" t="s">
         <v>314</v>
       </c>
-      <c r="B315" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C315">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A316" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D315">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A316" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B316" t="s">
         <v>315</v>
       </c>
-      <c r="B316" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C316">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A317" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D316">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A317" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B317" t="s">
         <v>316</v>
       </c>
-      <c r="B317" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C317">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A318" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D317">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A318" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B318" t="s">
         <v>317</v>
       </c>
-      <c r="B318" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C318">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A319" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D318">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A319" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B319" t="s">
         <v>318</v>
       </c>
-      <c r="B319" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C319">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A320" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D319">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A320" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B320" t="s">
         <v>319</v>
       </c>
-      <c r="B320" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C320">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A321" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D320">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A321" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B321" t="s">
         <v>320</v>
       </c>
-      <c r="B321" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C321">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A322" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D321">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A322" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B322" t="s">
         <v>321</v>
       </c>
-      <c r="B322" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C322">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A323" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D322">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A323" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B323" t="s">
         <v>322</v>
       </c>
-      <c r="B323" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C323">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A324" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D323">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A324" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B324" t="s">
         <v>323</v>
       </c>
-      <c r="B324" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C324">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A325" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D324">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A325" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B325" t="s">
         <v>324</v>
       </c>
-      <c r="B325" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C325">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A326" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D325">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A326" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B326" t="s">
         <v>325</v>
       </c>
-      <c r="B326" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C326">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A327" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D326">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A327" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B327" t="s">
         <v>326</v>
       </c>
-      <c r="B327" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C327">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A328" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D327">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A328" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B328" t="s">
         <v>327</v>
       </c>
-      <c r="B328" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C328">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A329" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D328">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A329" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B329" t="s">
         <v>328</v>
       </c>
-      <c r="B329" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C329">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A330" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D329">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A330" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B330" t="s">
         <v>329</v>
       </c>
-      <c r="B330" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C330">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A331" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D330">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A331" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B331" t="s">
         <v>330</v>
       </c>
-      <c r="B331" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C331">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A332" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D331">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A332" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B332" t="s">
         <v>331</v>
       </c>
-      <c r="B332" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C332">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A333" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D332">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A333" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B333" t="s">
         <v>332</v>
       </c>
-      <c r="B333" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C333">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A334" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D333">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A334" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B334" t="s">
         <v>333</v>
       </c>
-      <c r="B334" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C334">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A335" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D334">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A335" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B335" t="s">
         <v>334</v>
       </c>
-      <c r="B335" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C335">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A336" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D335">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A336" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B336" t="s">
         <v>335</v>
       </c>
-      <c r="B336" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C336">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A337" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D336">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A337" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B337" t="s">
         <v>336</v>
       </c>
-      <c r="B337" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C337">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A338" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D337">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A338" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B338" t="s">
         <v>337</v>
       </c>
-      <c r="B338" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C338">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A339" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D338">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A339" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B339" t="s">
         <v>338</v>
       </c>
-      <c r="B339" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C339">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A340" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D339">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A340" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B340" t="s">
         <v>339</v>
       </c>
-      <c r="B340" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C340">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A341" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D340">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A341" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B341" t="s">
         <v>340</v>
       </c>
-      <c r="B341" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C341">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A342" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D341">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A342" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B342" t="s">
         <v>341</v>
       </c>
-      <c r="B342" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C342">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A343" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D342">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A343" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B343" t="s">
         <v>342</v>
       </c>
-      <c r="B343" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C343">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A344" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D343">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A344" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B344" t="s">
         <v>343</v>
       </c>
-      <c r="B344" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C344">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A345" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D344">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A345" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B345" t="s">
         <v>344</v>
       </c>
-      <c r="B345" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C345">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A346" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D345">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A346" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B346" t="s">
         <v>345</v>
       </c>
-      <c r="B346" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C346">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A347" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D346">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A347" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B347" t="s">
         <v>346</v>
       </c>
-      <c r="B347" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C347">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A348" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D347">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A348" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B348" t="s">
         <v>347</v>
       </c>
-      <c r="B348" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C348">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A349" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D348">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A349" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B349" t="s">
         <v>348</v>
       </c>
-      <c r="B349" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C349">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A350" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D349">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A350" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B350" t="s">
         <v>349</v>
       </c>
-      <c r="B350" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C350">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A351" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D350">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A351" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B351" t="s">
         <v>350</v>
       </c>
-      <c r="B351" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C351">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A352" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D351">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A352" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B352" t="s">
         <v>351</v>
       </c>
-      <c r="B352" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C352">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A353" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D352">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A353" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B353" t="s">
         <v>352</v>
       </c>
-      <c r="B353" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C353">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A354" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D353">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A354" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B354" t="s">
         <v>353</v>
       </c>
-      <c r="B354" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C354">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A355" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D354">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A355" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B355" t="s">
         <v>354</v>
       </c>
-      <c r="B355" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C355">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A356" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D355">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A356" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B356" t="s">
         <v>355</v>
       </c>
-      <c r="B356" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C356">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A357" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D356">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A357" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B357" t="s">
         <v>356</v>
       </c>
-      <c r="B357" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C357">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A358" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D357">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A358" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B358" t="s">
         <v>357</v>
       </c>
-      <c r="B358" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C358">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A359" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D358">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A359" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B359" t="s">
         <v>358</v>
       </c>
-      <c r="B359" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C359">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A360" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D359">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A360" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B360" t="s">
         <v>359</v>
       </c>
-      <c r="B360" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C360">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A361" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D360">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A361" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B361" t="s">
         <v>360</v>
       </c>
-      <c r="B361" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C361">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A362" t="s">
+        <v>2E-3</v>
+      </c>
+      <c r="D361">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A362" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B362" t="s">
         <v>361</v>
       </c>
-      <c r="B362" s="2">
-        <v>2E-3</v>
-      </c>
       <c r="C362">
+        <v>2E-3</v>
+      </c>
+      <c r="D362">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
